--- a/report/mearsuring-profile/MP-03_Battery_Medium_Consumption.xlsx
+++ b/report/mearsuring-profile/MP-03_Battery_Medium_Consumption.xlsx
@@ -587,9 +587,8 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>▶  MP-03 Battery Medium - Consumption &amp; Regen (Giám Sát Năng Lượng &amp; Sức Khỏe Pin BMS)  |  Tests: LOAD-008, LOAD-010, PERF-004, PERF-008, END-012, SAFE-004
-Description (EN): Medium-frequency monitoring of battery management system (BMS) voltage, current, state of charge (SOC), health (SOH), energy charged/discharged, and temperatures.
-Mô tả (VI): Giám sát chu kỳ trung bình (1s-5s) điện áp, dòng điện, trạng thái sạc (SOC), sức khỏe pin (SOH), nhiệt độ cell cực đại/cực tiểu, điện trở trong và năng lượng sạc/xả tích lũy.</t>
+          <t>▶  MP-03 Battery Medium - Consumption &amp; Regen  |  Tests: LOAD-008, LOAD-010, PERF-004, PERF-008, END-012, SAFE-004
+Description: Medium-frequency monitoring of battery management system (BMS) voltage, current, state of charge (SOC), health (SOH), energy charged/discharged, and temperatures.</t>
         </is>
       </c>
     </row>

--- a/report/mearsuring-profile/MP-03_Battery_Medium_Consumption.xlsx
+++ b/report/mearsuring-profile/MP-03_Battery_Medium_Consumption.xlsx
@@ -583,8 +583,15 @@
   </sheetPr>
   <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18.28515625" customWidth="1" min="1" max="1"/>
+    <col width="42.7109375" customWidth="1" min="2" max="2"/>
+    <col width="29.28515625" customWidth="1" min="4" max="4"/>
+    <col width="13.42578125" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="34.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>▶  MP-03 Battery Medium - Consumption &amp; Regen  |  Tests: LOAD-008, LOAD-010, PERF-004, PERF-008, END-012, SAFE-004
@@ -644,7 +651,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
+    <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>bms_voltage</t>
@@ -688,7 +695,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>bms_current</t>
@@ -732,7 +739,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="72" customHeight="1">
+    <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>bms_soc</t>
@@ -776,7 +783,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>bat_soh_pct</t>
@@ -820,7 +827,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1">
+    <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>bat_energy_discharged_kwh</t>
@@ -864,7 +871,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>bat_energy_regen_kwh</t>
@@ -908,7 +915,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
+    <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>bat_temp_max</t>
@@ -952,7 +959,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
+    <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>bat_temp_min</t>
@@ -996,7 +1003,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>bat_cell_vmin</t>
@@ -1040,7 +1047,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>bat_cell_vmax</t>
@@ -1084,7 +1091,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
+    <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>bat_fault_code</t>
@@ -1128,7 +1135,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>bat_cycle_count</t>
@@ -1172,7 +1179,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1">
+    <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>bat_charge_power_kw</t>
@@ -1216,7 +1223,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1">
+    <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>ambient_temp</t>

--- a/report/mearsuring-profile/MP-03_Battery_Medium_Consumption.xlsx
+++ b/report/mearsuring-profile/MP-03_Battery_Medium_Consumption.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>no present</t>
+          <t>present</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>no present</t>
+          <t>present</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>no present</t>
+          <t>present</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>no present</t>
+          <t>present</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>no present</t>
+          <t>present</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>no present</t>
+          <t>present</t>
         </is>
       </c>
     </row>
@@ -1224,44 +1224,412 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>bmsa_voltage</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Battery Pack A terminal voltage</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>System/CANBusSystem/cBMSA/Voltage</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>250 ms</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>High speed Pack A voltage; PERF-008</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>bmsa_current</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Battery Pack A current (signed, +disch / -regen)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>System/CANBusSystem/cBMSA/Current</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-800</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>250 ms</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>High speed Pack A current; PERF-008</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>bmsa_soc</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Battery Pack A state of charge</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>System/CANBusSystem/cBMSA/SOC</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>1 s</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Pack A energy level; LOAD-010</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>bmsa_temp_max</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Battery Pack A maximum cell temperature</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>System/CANBusSystem/cBMSA/MaxTemp</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>5 s</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Pack A thermal monitoring</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>bmsb_voltage</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Battery Pack B terminal voltage</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>System/CANBusSystem/cBMSB/Voltage</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>250 ms</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>High speed Pack B voltage; PERF-008</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>bmsb_current</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Battery Pack B current (signed, +disch / -regen)</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>System/CANBusSystem/cBMSB/Current</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-800</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>250 ms</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>High speed Pack B current; PERF-008</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>bmsb_soc</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Battery Pack B state of charge</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>System/CANBusSystem/cBMSB/SOC</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>1 s</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Pack B energy level; LOAD-010</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>bmsb_temp_max</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Battery Pack B maximum cell temperature</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>System/CANBusSystem/cBMSB/MaxTemp</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>5 s</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Pack B thermal monitoring</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>ambient_temp</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Ambient temperature</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E24" s="10" t="n">
         <v>-20</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F24" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G24" s="13" t="n">
         <v>60000</v>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H24" s="11" t="n">
         <v>0.0167</v>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>Metric1m</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>manual-only</t>
         </is>

--- a/report/mearsuring-profile/MP-03_Battery_Medium_Consumption.xlsx
+++ b/report/mearsuring-profile/MP-03_Battery_Medium_Consumption.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -1410,41 +1410,41 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>bmsb_voltage</t>
+          <t>bmsa_soh</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Battery Pack B terminal voltage</t>
+          <t>Battery Pack A State of Health</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>System/CANBusSystem/cBMSB/Voltage</t>
+          <t>System/CANBusSystem/cBMSA/SOH</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>250 ms</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>4</v>
+        <v>1.16e-05</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>High speed Pack B voltage; PERF-008</t>
+          <t>Metric1d</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1456,29 +1456,29 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>bmsb_current</t>
+          <t>bmsb_voltage</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Battery Pack B current (signed, +disch / -regen)</t>
+          <t>Battery Pack B terminal voltage</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>System/CANBusSystem/cBMSB/Current</t>
+          <t>System/CANBusSystem/cBMSB/Voltage</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>High speed Pack B current; PERF-008</t>
+          <t>High speed Pack B voltage; PERF-008</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1502,41 +1502,41 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>bmsb_soc</t>
+          <t>bmsb_current</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Battery Pack B state of charge</t>
+          <t>Battery Pack B current (signed, +disch / -regen)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>System/CANBusSystem/cBMSB/SOC</t>
+          <t>System/CANBusSystem/cBMSB/Current</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>1 s</t>
+          <t>250 ms</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Pack B energy level; LOAD-010</t>
+          <t>High speed Pack B current; PERF-008</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1548,88 +1548,180 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>bmsb_soc</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Battery Pack B state of charge</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>System/CANBusSystem/cBMSB/SOC</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>1 s</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Pack B energy level; LOAD-010</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>bmsb_temp_max</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Battery Pack B maximum cell temperature</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>System/CANBusSystem/cBMSB/MaxTemp</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E24" s="5" t="n">
         <v>-20</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F24" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>5 s</t>
         </is>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="H24" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Pack B thermal monitoring</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>bmsb_soh</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Battery Pack B State of Health</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>System/CANBusSystem/cBMSB/SOH</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>1 day</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>1.16e-05</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Metric1d</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>ambient_temp</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Ambient temperature</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E26" s="10" t="n">
         <v>-20</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F26" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G26" s="13" t="n">
         <v>60000</v>
       </c>
-      <c r="H24" s="11" t="n">
+      <c r="H26" s="11" t="n">
         <v>0.0167</v>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>Metric1m</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>manual-only</t>
         </is>
